--- a/fmt/tests/condominium_import.xlsx
+++ b/fmt/tests/condominium_import.xlsx
@@ -562,76 +562,80 @@
       <protection locked="true" hidden="false"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="19">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="20" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="20" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -950,128 +954,128 @@
   <dimension ref="A1:R2"/>
   <sheetFormatPr defaultColWidth="9.00390625" defaultRowHeight="14.25" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="7.59"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="20.13"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="17.6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="19.26"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="5" style="0" width="14.6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="17.67"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="10.73"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="11"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="9.14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="9.86"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="0" width="21.4"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="0" width="18.4"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="0" width="17.73"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="0" width="17.14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="0" width="14.73"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="17" style="0" width="17"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="18" min="18" style="0" width="21.87"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="7.58"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="20.13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="17.61"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="19.26"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="5" style="1" width="14.6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="17.67"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="10.73"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="9.14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="1" width="9.86"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="1" width="21.4"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="1" width="18.4"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="1" width="17.73"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="1" width="17.15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="1" width="14.73"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="17" style="1" width="17"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="18" min="18" style="1" width="21.88"/>
   </cols>
   <sheetData>
-    <row r="1" s="4" customFormat="true" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+    <row r="1" s="5" customFormat="true" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="2" t="s">
+      <c r="B1" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="G1" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="H1" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="I1" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="J1" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="K1" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="L1" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="M1" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="3" t="s">
+      <c r="N1" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="3" t="s">
+      <c r="O1" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="3" t="s">
+      <c r="P1" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="3" t="s">
+      <c r="Q1" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="R1" s="3" t="s">
+      <c r="R1" s="4" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="n">
+      <c r="A2" s="1" t="n">
         <v>17</v>
       </c>
-      <c r="B2" s="0" t="s">
+      <c r="B2" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="C2" s="5" t="s">
+      <c r="C2" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="D2" s="6" t="s">
+      <c r="D2" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="E2" s="0" t="n">
+      <c r="E2" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="G2" s="6" t="s">
+      <c r="G2" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="H2" s="0" t="n">
+      <c r="H2" s="1" t="n">
         <v>1083</v>
       </c>
-      <c r="I2" s="6" t="s">
+      <c r="I2" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="J2" s="6" t="s">
+      <c r="J2" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="K2" s="6" t="s">
+      <c r="K2" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="L2" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="M2" s="0" t="n">
+      <c r="L2" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="M2" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="N2" s="7" t="n">
+      <c r="N2" s="8" t="n">
         <v>44743</v>
       </c>
-      <c r="O2" s="7" t="n">
+      <c r="O2" s="8" t="n">
         <v>45107</v>
       </c>
-      <c r="P2" s="6" t="s">
+      <c r="P2" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="Q2" s="6" t="s">
+      <c r="Q2" s="7" t="s">
         <v>26</v>
       </c>
     </row>
@@ -1096,41 +1100,41 @@
   <dimension ref="A1:C23"/>
   <sheetFormatPr defaultColWidth="9.00390625" defaultRowHeight="14.25" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="18.14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="23.26"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="24.13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="18.14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="23.26"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="24.13"/>
   </cols>
   <sheetData>
-    <row r="1" s="10" customFormat="true" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="10" t="s">
+    <row r="1" s="11" customFormat="true" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="11" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="10" t="s">
+      <c r="B1" s="11" t="s">
         <v>27</v>
       </c>
-      <c r="C1" s="10" t="s">
+      <c r="C1" s="11" t="s">
         <v>130</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="16" t="s">
+      <c r="A2" s="17" t="s">
         <v>131</v>
       </c>
-      <c r="B2" s="6" t="s">
+      <c r="B2" s="7" t="s">
         <v>132</v>
       </c>
-      <c r="C2" s="0" t="n">
+      <c r="C2" s="1" t="n">
         <v>1000</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="B3" s="0" t="s">
+      <c r="A3" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="B3" s="1" t="s">
         <v>133</v>
       </c>
-      <c r="C3" s="0" t="n">
+      <c r="C3" s="1" t="n">
         <v>1000</v>
       </c>
     </row>
@@ -1157,217 +1161,217 @@
   <dimension ref="A1:C19"/>
   <sheetFormatPr defaultColWidth="9.00390625" defaultRowHeight="14.25" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="10.13"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="17.14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="10.13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="17.15"/>
   </cols>
   <sheetData>
-    <row r="1" s="8" customFormat="true" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="8" t="s">
+    <row r="1" s="9" customFormat="true" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="9" t="s">
         <v>134</v>
       </c>
-      <c r="B1" s="8" t="s">
+      <c r="B1" s="9" t="s">
         <v>127</v>
       </c>
-      <c r="C1" s="8" t="s">
+      <c r="C1" s="9" t="s">
         <v>135</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="16" t="s">
+      <c r="A2" s="17" t="s">
         <v>131</v>
       </c>
-      <c r="B2" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="C2" s="0" t="n">
+      <c r="B2" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="C2" s="1" t="n">
         <v>163</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="16" t="s">
+      <c r="A3" s="17" t="s">
         <v>131</v>
       </c>
-      <c r="B3" s="0" t="n">
+      <c r="B3" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="C3" s="0" t="n">
+      <c r="C3" s="1" t="n">
         <v>163</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="16" t="s">
+      <c r="A4" s="17" t="s">
         <v>131</v>
       </c>
-      <c r="B4" s="0" t="n">
+      <c r="B4" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="C4" s="0" t="n">
+      <c r="C4" s="1" t="n">
         <v>124</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="16" t="s">
+      <c r="A5" s="17" t="s">
         <v>131</v>
       </c>
-      <c r="B5" s="0" t="n">
+      <c r="B5" s="1" t="n">
         <v>4</v>
       </c>
-      <c r="C5" s="0" t="n">
+      <c r="C5" s="1" t="n">
         <v>124</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="16" t="s">
+      <c r="A6" s="17" t="s">
         <v>131</v>
       </c>
-      <c r="B6" s="0" t="n">
+      <c r="B6" s="1" t="n">
         <v>5</v>
       </c>
-      <c r="C6" s="0" t="n">
+      <c r="C6" s="1" t="n">
         <v>263</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="16" t="s">
+      <c r="A7" s="17" t="s">
         <v>131</v>
       </c>
-      <c r="B7" s="0" t="n">
+      <c r="B7" s="1" t="n">
         <v>6</v>
       </c>
-      <c r="C7" s="0" t="n">
+      <c r="C7" s="1" t="n">
         <v>64</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="16" t="s">
+      <c r="A8" s="17" t="s">
         <v>131</v>
       </c>
-      <c r="B8" s="0" t="n">
+      <c r="B8" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="C8" s="0" t="n">
+      <c r="C8" s="1" t="n">
         <v>16</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="16" t="s">
+      <c r="A9" s="17" t="s">
         <v>131</v>
       </c>
-      <c r="B9" s="0" t="n">
+      <c r="B9" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="C9" s="0" t="n">
+      <c r="C9" s="1" t="n">
         <v>19</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="16" t="s">
+      <c r="A10" s="17" t="s">
         <v>131</v>
       </c>
-      <c r="B10" s="0" t="n">
+      <c r="B10" s="1" t="n">
         <v>9</v>
       </c>
-      <c r="C10" s="0" t="n">
+      <c r="C10" s="1" t="n">
         <v>64</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="B11" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="C11" s="0" t="n">
+      <c r="A11" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="B11" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="C11" s="1" t="n">
         <v>163</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="B12" s="0" t="n">
+      <c r="A12" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="B12" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="C12" s="0" t="n">
+      <c r="C12" s="1" t="n">
         <v>163</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="B13" s="0" t="n">
+      <c r="A13" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="B13" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="C13" s="0" t="n">
+      <c r="C13" s="1" t="n">
         <v>124</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="B14" s="0" t="n">
+      <c r="A14" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="B14" s="1" t="n">
         <v>4</v>
       </c>
-      <c r="C14" s="0" t="n">
+      <c r="C14" s="1" t="n">
         <v>124</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="B15" s="0" t="n">
+      <c r="A15" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="B15" s="1" t="n">
         <v>5</v>
       </c>
-      <c r="C15" s="0" t="n">
+      <c r="C15" s="1" t="n">
         <v>263</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="B16" s="0" t="n">
+      <c r="A16" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="B16" s="1" t="n">
         <v>6</v>
       </c>
-      <c r="C16" s="0" t="n">
+      <c r="C16" s="1" t="n">
         <v>64</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="B17" s="0" t="n">
+      <c r="A17" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="B17" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="C17" s="0" t="n">
+      <c r="C17" s="1" t="n">
         <v>16</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="B18" s="0" t="n">
+      <c r="A18" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="B18" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="C18" s="0" t="n">
+      <c r="C18" s="1" t="n">
         <v>19</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="B19" s="0" t="n">
+      <c r="A19" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="B19" s="1" t="n">
         <v>9</v>
       </c>
-      <c r="C19" s="0" t="n">
+      <c r="C19" s="1" t="n">
         <v>64</v>
       </c>
     </row>
@@ -1390,104 +1394,82 @@
   <dimension ref="A1:A26"/>
   <sheetFormatPr defaultColWidth="10.6796875" defaultRowHeight="14.25" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="14.26"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="14.26"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="10" t="s">
+      <c r="A1" s="11" t="s">
         <v>136</v>
       </c>
     </row>
-    <row r="2" s="17" customFormat="true" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="17" t="n">
+    <row r="2" s="18" customFormat="true" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="18" t="n">
         <v>1003</v>
       </c>
     </row>
-    <row r="3" s="17" customFormat="true" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="17" t="n">
-        <v>1012</v>
-      </c>
-    </row>
-    <row r="4" s="17" customFormat="true" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="17" t="n">
-        <v>1020</v>
-      </c>
-    </row>
-    <row r="5" s="17" customFormat="true" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="17" t="n">
-        <v>1049</v>
-      </c>
-    </row>
-    <row r="6" s="17" customFormat="true" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="17" t="n">
-        <v>1090</v>
-      </c>
-    </row>
+    <row r="3" s="18" customFormat="true" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="4" s="18" customFormat="true" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="5" s="18" customFormat="true" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="6" s="18" customFormat="true" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="7" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="17" t="n">
-        <v>1097</v>
-      </c>
+      <c r="A7" s="18"/>
     </row>
     <row r="8" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="17" t="n">
-        <v>1129</v>
-      </c>
+      <c r="A8" s="18"/>
     </row>
     <row r="9" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="17" t="n">
-        <v>1131</v>
-      </c>
+      <c r="A9" s="18"/>
     </row>
     <row r="10" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="17"/>
+      <c r="A10" s="18"/>
     </row>
     <row r="11" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="17"/>
+      <c r="A11" s="18"/>
     </row>
     <row r="12" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="17"/>
+      <c r="A12" s="18"/>
     </row>
     <row r="13" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="17"/>
+      <c r="A13" s="18"/>
     </row>
     <row r="14" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="17"/>
+      <c r="A14" s="18"/>
     </row>
     <row r="15" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="17"/>
+      <c r="A15" s="18"/>
     </row>
     <row r="16" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="17"/>
+      <c r="A16" s="18"/>
     </row>
     <row r="17" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="17"/>
+      <c r="A17" s="18"/>
     </row>
     <row r="18" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="17"/>
+      <c r="A18" s="18"/>
     </row>
     <row r="19" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="17"/>
+      <c r="A19" s="18"/>
     </row>
     <row r="20" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="17"/>
+      <c r="A20" s="18"/>
     </row>
     <row r="21" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="17"/>
+      <c r="A21" s="18"/>
     </row>
     <row r="22" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="17"/>
+      <c r="A22" s="18"/>
     </row>
     <row r="23" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="17"/>
+      <c r="A23" s="18"/>
     </row>
     <row r="24" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="17"/>
+      <c r="A24" s="18"/>
     </row>
     <row r="25" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="17"/>
+      <c r="A25" s="18"/>
     </row>
     <row r="26" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="17"/>
+      <c r="A26" s="18"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="A2:A26">
@@ -1511,51 +1493,51 @@
   <dimension ref="A1:D3"/>
   <sheetFormatPr defaultColWidth="9.00390625" defaultRowHeight="14.25" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="23.14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="34"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="23.4"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="23.14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="34"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="23.4"/>
   </cols>
   <sheetData>
-    <row r="1" s="4" customFormat="true" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+    <row r="1" s="5" customFormat="true" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="2" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="s">
+      <c r="A2" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="B2" s="0" t="s">
+      <c r="B2" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="C2" s="0" t="s">
+      <c r="C2" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="D2" s="0" t="n">
+      <c r="D2" s="1" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="0" t="s">
+      <c r="A3" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="B3" s="0" t="s">
+      <c r="B3" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="C3" s="0" t="s">
+      <c r="C3" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="D3" s="0" t="n">
+      <c r="D3" s="1" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1581,73 +1563,73 @@
   <sheetFormatPr defaultColWidth="10.6796875" defaultRowHeight="14.25" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="9" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="8" t="s">
+      <c r="B1" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="C1" s="9" t="s">
+      <c r="C1" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="D1" s="9" t="s">
+      <c r="D1" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="E1" s="9" t="s">
+      <c r="E1" s="10" t="s">
         <v>39</v>
       </c>
-      <c r="F1" s="9" t="s">
+      <c r="F1" s="10" t="s">
         <v>6</v>
       </c>
-      <c r="G1" s="9" t="s">
+      <c r="G1" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="H1" s="9" t="s">
+      <c r="H1" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="I1" s="9" t="s">
+      <c r="I1" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="J1" s="9" t="s">
+      <c r="J1" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="K1" s="9" t="s">
+      <c r="K1" s="10" t="s">
         <v>40</v>
       </c>
-      <c r="L1" s="9" t="s">
+      <c r="L1" s="10" t="s">
         <v>41</v>
       </c>
-      <c r="M1" s="9" t="s">
+      <c r="M1" s="10" t="s">
         <v>42</v>
       </c>
-      <c r="N1" s="9" t="s">
+      <c r="N1" s="10" t="s">
         <v>43</v>
       </c>
-      <c r="O1" s="9" t="s">
+      <c r="O1" s="10" t="s">
         <v>44</v>
       </c>
-      <c r="P1" s="9" t="s">
+      <c r="P1" s="10" t="s">
         <v>45</v>
       </c>
-      <c r="Q1" s="9" t="s">
+      <c r="Q1" s="10" t="s">
         <v>46</v>
       </c>
-      <c r="R1" s="9" t="s">
+      <c r="R1" s="10" t="s">
         <v>47</v>
       </c>
-      <c r="S1" s="10" t="s">
+      <c r="S1" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="T1" s="10" t="s">
+      <c r="T1" s="11" t="s">
         <v>49</v>
       </c>
-      <c r="U1" s="10" t="s">
+      <c r="U1" s="11" t="s">
         <v>50</v>
       </c>
-      <c r="V1" s="10" t="s">
+      <c r="V1" s="11" t="s">
         <v>5</v>
       </c>
-      <c r="W1" s="10" t="s">
+      <c r="W1" s="11" t="s">
         <v>2</v>
       </c>
     </row>
@@ -1670,290 +1652,290 @@
   <dimension ref="A1:W6"/>
   <sheetFormatPr defaultColWidth="9.00390625" defaultRowHeight="14.25" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="13.14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="33"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="19"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="17.73"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="25.53"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="7" style="0" width="22.4"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="9" style="0" width="16.13"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="11" style="0" width="16.59"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="13" style="0" width="20"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="0" width="27.14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="0" width="18.87"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="18" min="17" style="0" width="18"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="19" min="19" style="0" width="15.73"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="20" min="20" style="0" width="22.87"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="21" min="21" style="0" width="21.73"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="22" min="22" style="0" width="17.73"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="23" min="23" style="0" width="23.4"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="13.15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="33"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="19"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="17.73"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="25.53"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="7" style="1" width="22.4"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="9" style="1" width="16.12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="11" style="1" width="16.58"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="13" style="1" width="20"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="1" width="27.15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="1" width="18.87"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="18" min="17" style="1" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="19" min="19" style="1" width="15.73"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="20" min="20" style="1" width="22.88"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="21" min="21" style="1" width="21.73"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="22" min="22" style="1" width="17.73"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="23" min="23" style="1" width="23.4"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="9" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="8" t="s">
+      <c r="B1" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="C1" s="11" t="s">
+      <c r="C1" s="12" t="s">
         <v>37</v>
       </c>
-      <c r="D1" s="11" t="s">
+      <c r="D1" s="12" t="s">
         <v>38</v>
       </c>
-      <c r="E1" s="11" t="s">
+      <c r="E1" s="12" t="s">
         <v>39</v>
       </c>
-      <c r="F1" s="11" t="s">
+      <c r="F1" s="12" t="s">
         <v>6</v>
       </c>
-      <c r="G1" s="11" t="s">
+      <c r="G1" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="H1" s="11" t="s">
+      <c r="H1" s="12" t="s">
         <v>8</v>
       </c>
-      <c r="I1" s="11" t="s">
+      <c r="I1" s="12" t="s">
         <v>9</v>
       </c>
-      <c r="J1" s="9" t="s">
+      <c r="J1" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="K1" s="9" t="s">
+      <c r="K1" s="10" t="s">
         <v>40</v>
       </c>
-      <c r="L1" s="9" t="s">
+      <c r="L1" s="10" t="s">
         <v>41</v>
       </c>
-      <c r="M1" s="9" t="s">
+      <c r="M1" s="10" t="s">
         <v>42</v>
       </c>
-      <c r="N1" s="9" t="s">
+      <c r="N1" s="10" t="s">
         <v>43</v>
       </c>
-      <c r="O1" s="9" t="s">
+      <c r="O1" s="10" t="s">
         <v>44</v>
       </c>
-      <c r="P1" s="9" t="s">
+      <c r="P1" s="10" t="s">
         <v>45</v>
       </c>
-      <c r="Q1" s="9" t="s">
+      <c r="Q1" s="10" t="s">
         <v>46</v>
       </c>
-      <c r="R1" s="9" t="s">
+      <c r="R1" s="10" t="s">
         <v>47</v>
       </c>
-      <c r="S1" s="10" t="s">
+      <c r="S1" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="T1" s="10" t="s">
+      <c r="T1" s="11" t="s">
         <v>49</v>
       </c>
-      <c r="U1" s="10" t="s">
+      <c r="U1" s="11" t="s">
         <v>50</v>
       </c>
-      <c r="V1" s="10" t="s">
+      <c r="V1" s="11" t="s">
         <v>5</v>
       </c>
-      <c r="W1" s="10" t="s">
+      <c r="W1" s="11" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="B2" s="0" t="s">
+      <c r="A2" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="C2" s="0" t="s">
+      <c r="C2" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="D2" s="0" t="s">
+      <c r="D2" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="E2" s="0" t="s">
+      <c r="E2" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="F2" s="0" t="s">
+      <c r="F2" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="G2" s="0" t="n">
+      <c r="G2" s="1" t="n">
         <v>1083</v>
       </c>
-      <c r="H2" s="0" t="s">
+      <c r="H2" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="I2" s="0" t="s">
+      <c r="I2" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="J2" s="0" t="s">
+      <c r="J2" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="M2" s="6" t="s">
+      <c r="M2" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="O2" s="6" t="s">
+      <c r="O2" s="7" t="s">
         <v>57</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="0" t="n">
+      <c r="A3" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="B3" s="0" t="s">
+      <c r="B3" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="C3" s="0" t="s">
+      <c r="C3" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="D3" s="0" t="s">
+      <c r="D3" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="E3" s="0" t="s">
+      <c r="E3" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="F3" s="0" t="s">
+      <c r="F3" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="G3" s="0" t="n">
+      <c r="G3" s="1" t="n">
         <v>9880</v>
       </c>
-      <c r="H3" s="0" t="s">
+      <c r="H3" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="I3" s="0" t="s">
+      <c r="I3" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="J3" s="0" t="s">
+      <c r="J3" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="M3" s="6" t="s">
+      <c r="M3" s="7" t="s">
         <v>63</v>
       </c>
-      <c r="O3" s="6" t="s">
+      <c r="O3" s="7" t="s">
         <v>64</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="0" t="n">
+      <c r="A4" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="B4" s="0" t="s">
+      <c r="B4" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="C4" s="0" t="s">
+      <c r="C4" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="D4" s="0" t="s">
+      <c r="D4" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="E4" s="0" t="s">
+      <c r="E4" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="F4" s="0" t="s">
+      <c r="F4" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="G4" s="0" t="n">
+      <c r="G4" s="1" t="n">
         <v>1083</v>
       </c>
-      <c r="H4" s="0" t="s">
+      <c r="H4" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="I4" s="0" t="s">
+      <c r="I4" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="J4" s="0" t="s">
+      <c r="J4" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="M4" s="6" t="s">
+      <c r="M4" s="7" t="s">
         <v>68</v>
       </c>
-      <c r="O4" s="6" t="s">
+      <c r="O4" s="7" t="s">
         <v>69</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="0" t="n">
+      <c r="A5" s="1" t="n">
         <v>4</v>
       </c>
-      <c r="B5" s="0" t="s">
+      <c r="B5" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="C5" s="0" t="s">
+      <c r="C5" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="D5" s="0" t="s">
+      <c r="D5" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="E5" s="0" t="s">
+      <c r="E5" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="F5" s="0" t="s">
+      <c r="F5" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="G5" s="0" t="n">
+      <c r="G5" s="1" t="n">
         <v>1083</v>
       </c>
-      <c r="H5" s="0" t="s">
+      <c r="H5" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="I5" s="0" t="s">
+      <c r="I5" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="J5" s="0" t="s">
+      <c r="J5" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="K5" s="6" t="s">
+      <c r="K5" s="7" t="s">
         <v>73</v>
       </c>
-      <c r="M5" s="12" t="s">
+      <c r="M5" s="13" t="s">
         <v>74</v>
       </c>
-      <c r="O5" s="6" t="s">
+      <c r="O5" s="7" t="s">
         <v>75</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="0" t="n">
+      <c r="A6" s="1" t="n">
         <v>5</v>
       </c>
-      <c r="B6" s="0" t="s">
+      <c r="B6" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="C6" s="0" t="s">
+      <c r="C6" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="D6" s="0" t="s">
+      <c r="D6" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="E6" s="0" t="s">
+      <c r="E6" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="F6" s="0" t="s">
+      <c r="F6" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="G6" s="0" t="n">
+      <c r="G6" s="1" t="n">
         <v>1083</v>
       </c>
-      <c r="H6" s="0" t="s">
+      <c r="H6" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="I6" s="0" t="s">
+      <c r="I6" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="J6" s="0" t="s">
+      <c r="J6" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="K6" s="6" t="s">
+      <c r="K6" s="7" t="s">
         <v>79</v>
       </c>
-      <c r="M6" s="12" t="s">
+      <c r="M6" s="13" t="s">
         <v>80</v>
       </c>
-      <c r="O6" s="12" t="s">
+      <c r="O6" s="13" t="s">
         <v>81</v>
       </c>
     </row>
@@ -1982,108 +1964,108 @@
   <dimension ref="A1:H6"/>
   <sheetFormatPr defaultColWidth="9.00390625" defaultRowHeight="14.25" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="16.39"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="13.14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="23.26"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="23.87"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="18.26"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="6" style="0" width="31.14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="23"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="16.39"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="13.15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="23.26"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="23.87"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="18.26"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="6" style="1" width="31.15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="23"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="10" t="s">
+      <c r="A1" s="11" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="10" t="s">
+      <c r="B1" s="11" t="s">
         <v>82</v>
       </c>
-      <c r="C1" s="13" t="s">
+      <c r="C1" s="14" t="s">
         <v>83</v>
       </c>
-      <c r="D1" s="13" t="s">
+      <c r="D1" s="14" t="s">
         <v>84</v>
       </c>
-      <c r="E1" s="13" t="s">
+      <c r="E1" s="14" t="s">
         <v>85</v>
       </c>
-      <c r="F1" s="14" t="s">
+      <c r="F1" s="15" t="s">
         <v>86</v>
       </c>
-      <c r="G1" s="14" t="s">
+      <c r="G1" s="15" t="s">
         <v>87</v>
       </c>
-      <c r="H1" s="10" t="s">
+      <c r="H1" s="11" t="s">
         <v>88</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="B2" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="C2" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="F2" s="0" t="n">
+      <c r="A2" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="C2" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="F2" s="1" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="0" t="n">
+      <c r="A3" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="B3" s="0" t="n">
+      <c r="B3" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="C3" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="F3" s="0" t="n">
+      <c r="C3" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="F3" s="1" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="0" t="n">
+      <c r="A4" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="B4" s="0" t="n">
+      <c r="B4" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="C4" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="F4" s="0" t="n">
+      <c r="C4" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="F4" s="1" t="n">
         <v>3</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="0" t="n">
+      <c r="A5" s="1" t="n">
         <v>4</v>
       </c>
-      <c r="B5" s="0" t="n">
+      <c r="B5" s="1" t="n">
         <v>4</v>
       </c>
-      <c r="C5" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="F5" s="0" t="n">
+      <c r="C5" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="F5" s="1" t="n">
         <v>4</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="0" t="n">
+      <c r="A6" s="1" t="n">
         <v>5</v>
       </c>
-      <c r="B6" s="0" t="n">
+      <c r="B6" s="1" t="n">
         <v>5</v>
       </c>
-      <c r="C6" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="F6" s="0" t="n">
+      <c r="C6" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="F6" s="1" t="n">
         <v>5</v>
       </c>
     </row>
@@ -2108,151 +2090,151 @@
   <dimension ref="A1:G6"/>
   <sheetFormatPr defaultColWidth="9.00390625" defaultRowHeight="14.25" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="18"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="23.73"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="27.87"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="21.13"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="15.26"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="26.26"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="48.4"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="16.26"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="23.73"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="27.87"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="21.12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="15.26"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="26.26"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="48.4"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="16.26"/>
   </cols>
   <sheetData>
-    <row r="1" s="10" customFormat="true" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="10" t="s">
+    <row r="1" s="11" customFormat="true" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="11" t="s">
         <v>89</v>
       </c>
-      <c r="B1" s="10" t="s">
+      <c r="B1" s="11" t="s">
         <v>90</v>
       </c>
-      <c r="C1" s="10" t="s">
+      <c r="C1" s="11" t="s">
         <v>91</v>
       </c>
-      <c r="D1" s="10" t="s">
+      <c r="D1" s="11" t="s">
         <v>92</v>
       </c>
-      <c r="E1" s="10" t="s">
+      <c r="E1" s="11" t="s">
         <v>93</v>
       </c>
-      <c r="F1" s="10" t="s">
+      <c r="F1" s="11" t="s">
         <v>94</v>
       </c>
-      <c r="G1" s="10" t="s">
+      <c r="G1" s="11" t="s">
         <v>95</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="B2" s="0" t="s">
+      <c r="A2" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="C2" s="0" t="s">
+      <c r="C2" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="D2" s="0" t="s">
+      <c r="D2" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="E2" s="0" t="s">
+      <c r="E2" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="F2" s="0" t="s">
+      <c r="F2" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="G2" s="0" t="s">
+      <c r="G2" s="1" t="s">
         <v>97</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="0" t="n">
+      <c r="A3" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="B3" s="0" t="s">
+      <c r="B3" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="C3" s="0" t="s">
+      <c r="C3" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="D3" s="0" t="s">
+      <c r="D3" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="E3" s="0" t="s">
+      <c r="E3" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="F3" s="0" t="s">
+      <c r="F3" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="G3" s="0" t="s">
+      <c r="G3" s="1" t="s">
         <v>98</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="0" t="n">
+      <c r="A4" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="B4" s="0" t="s">
+      <c r="B4" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="C4" s="0" t="s">
+      <c r="C4" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="D4" s="0" t="s">
+      <c r="D4" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="E4" s="0" t="s">
+      <c r="E4" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="F4" s="0" t="s">
+      <c r="F4" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="G4" s="0" t="s">
+      <c r="G4" s="1" t="s">
         <v>99</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="0" t="n">
+      <c r="A5" s="1" t="n">
         <v>4</v>
       </c>
-      <c r="B5" s="0" t="s">
+      <c r="B5" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="C5" s="0" t="s">
+      <c r="C5" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="D5" s="0" t="s">
+      <c r="D5" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="E5" s="0" t="s">
+      <c r="E5" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="F5" s="0" t="s">
+      <c r="F5" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="G5" s="0" t="s">
+      <c r="G5" s="1" t="s">
         <v>100</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="0" t="n">
+      <c r="A6" s="1" t="n">
         <v>5</v>
       </c>
-      <c r="B6" s="0" t="s">
+      <c r="B6" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="C6" s="0" t="s">
+      <c r="C6" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="D6" s="0" t="s">
+      <c r="D6" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="E6" s="0" t="s">
+      <c r="E6" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="F6" s="0" t="s">
+      <c r="F6" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="G6" s="0" t="s">
+      <c r="G6" s="1" t="s">
         <v>101</v>
       </c>
     </row>
@@ -2277,51 +2259,51 @@
   <dimension ref="A1:F2"/>
   <sheetFormatPr defaultColWidth="9.00390625" defaultRowHeight="14.25" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="11.26"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="11.47"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="22.4"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="19"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="12.14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="12.73"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="11.26"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="11.47"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="22.4"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="19"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="12.15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="12.73"/>
   </cols>
   <sheetData>
-    <row r="1" s="10" customFormat="true" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="10" t="s">
+    <row r="1" s="11" customFormat="true" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="11" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="10" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="10" t="s">
+      <c r="B1" s="11" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="D1" s="10" t="s">
+      <c r="D1" s="11" t="s">
         <v>7</v>
       </c>
-      <c r="E1" s="10" t="s">
+      <c r="E1" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="F1" s="10" t="s">
+      <c r="F1" s="11" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="B2" s="0" t="s">
+      <c r="A2" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="C2" s="0" t="s">
+      <c r="C2" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="D2" s="0" t="n">
+      <c r="D2" s="1" t="n">
         <v>1083</v>
       </c>
-      <c r="E2" s="0" t="s">
+      <c r="E2" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="F2" s="0" t="s">
+      <c r="F2" s="1" t="s">
         <v>23</v>
       </c>
     </row>
@@ -2344,252 +2326,252 @@
   <dimension ref="A1:J15"/>
   <sheetFormatPr defaultColWidth="9.00390625" defaultRowHeight="14.25" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="15.73"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="2" style="0" width="17.73"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="20.26"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="23.14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="15.73"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="2" style="1" width="17.73"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="20.26"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="23.14"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="13" t="s">
+      <c r="A1" s="14" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="13" t="s">
+      <c r="B1" s="14" t="s">
         <v>102</v>
       </c>
-      <c r="C1" s="13" t="s">
+      <c r="C1" s="14" t="s">
         <v>103</v>
       </c>
-      <c r="D1" s="13" t="s">
+      <c r="D1" s="14" t="s">
         <v>104</v>
       </c>
-      <c r="E1" s="13" t="s">
+      <c r="E1" s="14" t="s">
         <v>105</v>
       </c>
-      <c r="F1" s="13" t="s">
+      <c r="F1" s="14" t="s">
         <v>106</v>
       </c>
-      <c r="G1" s="13" t="s">
+      <c r="G1" s="14" t="s">
         <v>107</v>
       </c>
-      <c r="H1" s="13" t="s">
+      <c r="H1" s="14" t="s">
         <v>108</v>
       </c>
-      <c r="I1" s="13" t="s">
+      <c r="I1" s="14" t="s">
         <v>109</v>
       </c>
-      <c r="J1" s="13" t="s">
+      <c r="J1" s="14" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="B2" s="0" t="s">
+      <c r="A2" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" s="1" t="s">
         <v>110</v>
       </c>
-      <c r="C2" s="0" t="s">
+      <c r="C2" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="D2" s="0" t="n">
+      <c r="D2" s="1" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="0" t="n">
+      <c r="A3" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="B3" s="0" t="s">
+      <c r="B3" s="1" t="s">
         <v>112</v>
       </c>
-      <c r="C3" s="0" t="s">
+      <c r="C3" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="D3" s="0" t="n">
+      <c r="D3" s="1" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="0" t="n">
+      <c r="A4" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="B4" s="0" t="s">
+      <c r="B4" s="1" t="s">
         <v>113</v>
       </c>
-      <c r="C4" s="0" t="s">
+      <c r="C4" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="D4" s="0" t="n">
+      <c r="D4" s="1" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="0" t="n">
+      <c r="A5" s="1" t="n">
         <v>4</v>
       </c>
-      <c r="B5" s="0" t="s">
+      <c r="B5" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="C5" s="0" t="s">
+      <c r="C5" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="D5" s="0" t="n">
+      <c r="D5" s="1" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="0" t="n">
+      <c r="A6" s="1" t="n">
         <v>5</v>
       </c>
-      <c r="B6" s="0" t="s">
+      <c r="B6" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="C6" s="0" t="s">
+      <c r="C6" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="D6" s="0" t="n">
+      <c r="D6" s="1" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="0" t="n">
+      <c r="A7" s="1" t="n">
         <v>6</v>
       </c>
-      <c r="B7" s="0" t="s">
+      <c r="B7" s="1" t="s">
         <v>116</v>
       </c>
-      <c r="C7" s="0" t="s">
+      <c r="C7" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="D7" s="0" t="n">
+      <c r="D7" s="1" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="0" t="n">
+      <c r="A8" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="B8" s="0" t="s">
+      <c r="B8" s="1" t="s">
         <v>117</v>
       </c>
-      <c r="C8" s="0" t="s">
+      <c r="C8" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="D8" s="0" t="n">
+      <c r="D8" s="1" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="0" t="n">
+      <c r="A9" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="B9" s="0" t="s">
+      <c r="B9" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="C9" s="0" t="s">
+      <c r="C9" s="1" t="s">
         <v>119</v>
       </c>
-      <c r="D9" s="0" t="n">
+      <c r="D9" s="1" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="0" t="n">
+      <c r="A10" s="1" t="n">
         <v>9</v>
       </c>
-      <c r="B10" s="0" t="s">
+      <c r="B10" s="1" t="s">
         <v>120</v>
       </c>
-      <c r="C10" s="0" t="s">
+      <c r="C10" s="1" t="s">
         <v>119</v>
       </c>
-      <c r="D10" s="0" t="n">
+      <c r="D10" s="1" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="0" t="n">
+      <c r="A11" s="1" t="n">
         <v>10</v>
       </c>
-      <c r="B11" s="0" t="s">
+      <c r="B11" s="1" t="s">
         <v>121</v>
       </c>
-      <c r="C11" s="0" t="s">
+      <c r="C11" s="1" t="s">
         <v>122</v>
       </c>
-      <c r="D11" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="I11" s="0" t="n">
+      <c r="D11" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="I11" s="1" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="0" t="n">
+      <c r="A12" s="1" t="n">
         <v>11</v>
       </c>
-      <c r="B12" s="0" t="s">
+      <c r="B12" s="1" t="s">
         <v>123</v>
       </c>
-      <c r="C12" s="0" t="s">
+      <c r="C12" s="1" t="s">
         <v>122</v>
       </c>
-      <c r="D12" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="I12" s="0" t="n">
+      <c r="D12" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="I12" s="1" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="0" t="n">
+      <c r="A13" s="1" t="n">
         <v>12</v>
       </c>
-      <c r="B13" s="0" t="s">
+      <c r="B13" s="1" t="s">
         <v>124</v>
       </c>
-      <c r="C13" s="0" t="s">
+      <c r="C13" s="1" t="s">
         <v>122</v>
       </c>
-      <c r="D13" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="I13" s="0" t="n">
+      <c r="D13" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="I13" s="1" t="n">
         <v>3</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="0" t="n">
+      <c r="A14" s="1" t="n">
         <v>13</v>
       </c>
-      <c r="B14" s="0" t="s">
+      <c r="B14" s="1" t="s">
         <v>125</v>
       </c>
-      <c r="C14" s="0" t="s">
+      <c r="C14" s="1" t="s">
         <v>122</v>
       </c>
-      <c r="D14" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="I14" s="0" t="n">
+      <c r="D14" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="I14" s="1" t="n">
         <v>4</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="0" t="n">
+      <c r="A15" s="1" t="n">
         <v>14</v>
       </c>
-      <c r="B15" s="0" t="s">
+      <c r="B15" s="1" t="s">
         <v>126</v>
       </c>
-      <c r="C15" s="0" t="s">
+      <c r="C15" s="1" t="s">
         <v>122</v>
       </c>
-      <c r="D15" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="I15" s="0" t="n">
+      <c r="D15" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="I15" s="1" t="n">
         <v>5</v>
       </c>
     </row>
@@ -2614,181 +2596,181 @@
   <dimension ref="A1:D15"/>
   <sheetFormatPr defaultColWidth="9.00390625" defaultRowHeight="14.25" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="11"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="18"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="12.6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="10.4"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="12.61"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="10.4"/>
   </cols>
   <sheetData>
-    <row r="1" s="10" customFormat="true" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="10" t="s">
+    <row r="1" s="11" customFormat="true" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="11" t="s">
         <v>127</v>
       </c>
-      <c r="B1" s="10" t="s">
+      <c r="B1" s="11" t="s">
         <v>89</v>
       </c>
-      <c r="C1" s="10" t="s">
+      <c r="C1" s="11" t="s">
         <v>128</v>
       </c>
-      <c r="D1" s="10" t="s">
+      <c r="D1" s="11" t="s">
         <v>129</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="B2" s="0" t="n">
+      <c r="A2" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" s="1" t="n">
         <v>4</v>
       </c>
-      <c r="C2" s="15" t="n">
+      <c r="C2" s="16" t="n">
         <v>44743</v>
       </c>
-      <c r="D2" s="15"/>
+      <c r="D2" s="16"/>
     </row>
     <row r="3" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="0" t="n">
+      <c r="A3" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="B3" s="0" t="n">
+      <c r="B3" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="C3" s="15" t="n">
+      <c r="C3" s="16" t="n">
         <v>44743</v>
       </c>
-      <c r="D3" s="15"/>
+      <c r="D3" s="16"/>
     </row>
     <row r="4" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="0" t="n">
+      <c r="A4" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="B4" s="0" t="n">
+      <c r="B4" s="1" t="n">
         <v>5</v>
       </c>
-      <c r="C4" s="15" t="n">
+      <c r="C4" s="16" t="n">
         <v>44743</v>
       </c>
-      <c r="D4" s="15"/>
+      <c r="D4" s="16"/>
     </row>
     <row r="5" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="0" t="n">
+      <c r="A5" s="1" t="n">
         <v>4</v>
       </c>
-      <c r="B5" s="0" t="n">
+      <c r="B5" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="C5" s="15" t="n">
+      <c r="C5" s="16" t="n">
         <v>44743</v>
       </c>
-      <c r="D5" s="15"/>
+      <c r="D5" s="16"/>
     </row>
     <row r="6" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="0" t="n">
+      <c r="A6" s="1" t="n">
         <v>5</v>
       </c>
-      <c r="B6" s="0" t="n">
+      <c r="B6" s="1" t="n">
         <v>4</v>
       </c>
-      <c r="C6" s="15" t="n">
+      <c r="C6" s="16" t="n">
         <v>44743</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="0" t="n">
+      <c r="A7" s="1" t="n">
         <v>6</v>
       </c>
-      <c r="B7" s="0" t="n">
+      <c r="B7" s="1" t="n">
         <v>4</v>
       </c>
-      <c r="C7" s="15" t="n">
+      <c r="C7" s="16" t="n">
         <v>44743</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="0" t="n">
+      <c r="A8" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="B8" s="0" t="n">
+      <c r="B8" s="1" t="n">
         <v>4</v>
       </c>
-      <c r="C8" s="15" t="n">
+      <c r="C8" s="16" t="n">
         <v>44743</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="0" t="n">
+      <c r="A9" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="B9" s="0" t="n">
+      <c r="B9" s="1" t="n">
         <v>5</v>
       </c>
-      <c r="C9" s="15" t="n">
+      <c r="C9" s="16" t="n">
         <v>44743</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="0" t="n">
+      <c r="A10" s="1" t="n">
         <v>9</v>
       </c>
-      <c r="B10" s="0" t="n">
+      <c r="B10" s="1" t="n">
         <v>4</v>
       </c>
-      <c r="C10" s="15" t="n">
+      <c r="C10" s="16" t="n">
         <v>44743</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="0" t="n">
+      <c r="A11" s="1" t="n">
         <v>10</v>
       </c>
-      <c r="B11" s="0" t="n">
+      <c r="B11" s="1" t="n">
         <v>4</v>
       </c>
-      <c r="C11" s="15" t="n">
+      <c r="C11" s="16" t="n">
         <v>44743</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="0" t="n">
+      <c r="A12" s="1" t="n">
         <v>11</v>
       </c>
-      <c r="B12" s="0" t="n">
+      <c r="B12" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="C12" s="15" t="n">
+      <c r="C12" s="16" t="n">
         <v>44743</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="0" t="n">
+      <c r="A13" s="1" t="n">
         <v>12</v>
       </c>
-      <c r="B13" s="0" t="n">
+      <c r="B13" s="1" t="n">
         <v>5</v>
       </c>
-      <c r="C13" s="15" t="n">
+      <c r="C13" s="16" t="n">
         <v>44743</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="0" t="n">
+      <c r="A14" s="1" t="n">
         <v>13</v>
       </c>
-      <c r="B14" s="0" t="n">
+      <c r="B14" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="C14" s="15" t="n">
+      <c r="C14" s="16" t="n">
         <v>44743</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="0" t="n">
+      <c r="A15" s="1" t="n">
         <v>14</v>
       </c>
-      <c r="B15" s="0" t="n">
+      <c r="B15" s="1" t="n">
         <v>4</v>
       </c>
-      <c r="C15" s="15" t="n">
+      <c r="C15" s="16" t="n">
         <v>44743</v>
       </c>
     </row>

--- a/fmt/tests/condominium_import.xlsx
+++ b/fmt/tests/condominium_import.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\DEV\wamp64\www\fmt-yb\packages\fmt\tests\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7DC91331-5512-4389-A25C-105C4F682476}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D761F1A-AB86-4B8A-A6C3-7D22E5134BB3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="45" windowWidth="28800" windowHeight="15435" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="45" windowWidth="28800" windowHeight="15435" tabRatio="739" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Condominium" sheetId="1" r:id="rId1"/>
@@ -81,9 +81,6 @@
     <t>lang</t>
   </si>
   <si>
-    <t>condo_manager_code</t>
-  </si>
-  <si>
     <t>accountant_code</t>
   </si>
   <si>
@@ -457,6 +454,9 @@
   </si>
   <si>
     <t>supplier_code</t>
+  </si>
+  <si>
+    <t>manager_code</t>
   </si>
 </sst>
 </file>
@@ -465,7 +465,7 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
     <numFmt numFmtId="164" formatCode="0000000000"/>
-    <numFmt numFmtId="166" formatCode="dd/mm/yyyy;@"/>
+    <numFmt numFmtId="165" formatCode="dd/mm/yyyy;@"/>
   </numFmts>
   <fonts count="4" x14ac:knownFonts="1">
     <font>
@@ -565,7 +565,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -867,7 +867,7 @@
     <col min="13" max="13" width="18.42578125" customWidth="1"/>
     <col min="14" max="14" width="17.7109375" style="17" customWidth="1"/>
     <col min="15" max="15" width="17.140625" style="17" customWidth="1"/>
-    <col min="16" max="16" width="14.7109375" customWidth="1"/>
+    <col min="16" max="16" width="24.28515625" customWidth="1"/>
     <col min="17" max="17" width="17" customWidth="1"/>
     <col min="18" max="18" width="21.85546875" customWidth="1"/>
   </cols>
@@ -907,25 +907,25 @@
         <v>10</v>
       </c>
       <c r="L1" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="M1" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="N1" s="16" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="16" t="s">
+      <c r="O1" s="16" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="16" t="s">
+      <c r="P1" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="3" t="s">
+      <c r="Q1" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="3" t="s">
+      <c r="R1" s="3" t="s">
         <v>16</v>
-      </c>
-      <c r="R1" s="3" t="s">
-        <v>17</v>
       </c>
     </row>
     <row r="2" spans="1:18" x14ac:dyDescent="0.25">
@@ -933,31 +933,31 @@
         <v>17</v>
       </c>
       <c r="B2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C2" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="C2" s="5" t="s">
+      <c r="D2" t="s">
         <v>19</v>
-      </c>
-      <c r="D2" t="s">
-        <v>20</v>
       </c>
       <c r="E2">
         <v>0</v>
       </c>
       <c r="G2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H2">
         <v>1083</v>
       </c>
       <c r="I2" t="s">
+        <v>21</v>
+      </c>
+      <c r="J2" t="s">
         <v>22</v>
       </c>
-      <c r="J2" t="s">
+      <c r="K2" t="s">
         <v>23</v>
-      </c>
-      <c r="K2" t="s">
-        <v>24</v>
       </c>
       <c r="L2">
         <v>1</v>
@@ -972,10 +972,10 @@
         <v>45107</v>
       </c>
       <c r="P2" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q2" t="s">
         <v>25</v>
-      </c>
-      <c r="Q2" t="s">
-        <v>26</v>
       </c>
     </row>
   </sheetData>
@@ -1000,18 +1000,18 @@
         <v>0</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="14" t="s">
+        <v>130</v>
+      </c>
+      <c r="B2" t="s">
         <v>131</v>
-      </c>
-      <c r="B2" t="s">
-        <v>132</v>
       </c>
       <c r="C2">
         <v>1000</v>
@@ -1022,7 +1022,7 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C3">
         <v>1000</v>
@@ -1049,18 +1049,18 @@
   <sheetData>
     <row r="1" spans="1:3" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
+        <v>133</v>
+      </c>
+      <c r="B1" s="6" t="s">
+        <v>126</v>
+      </c>
+      <c r="C1" s="6" t="s">
         <v>134</v>
-      </c>
-      <c r="B1" s="6" t="s">
-        <v>127</v>
-      </c>
-      <c r="C1" s="6" t="s">
-        <v>135</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="14" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B2">
         <v>1</v>
@@ -1071,7 +1071,7 @@
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="14" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B3">
         <v>2</v>
@@ -1082,7 +1082,7 @@
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="14" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B4">
         <v>3</v>
@@ -1093,7 +1093,7 @@
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="14" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B5">
         <v>4</v>
@@ -1104,7 +1104,7 @@
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="14" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B6">
         <v>5</v>
@@ -1115,7 +1115,7 @@
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" s="14" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B7">
         <v>6</v>
@@ -1126,7 +1126,7 @@
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="14" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B8">
         <v>7</v>
@@ -1137,7 +1137,7 @@
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" s="14" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B9">
         <v>8</v>
@@ -1148,7 +1148,7 @@
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" s="14" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B10">
         <v>9</v>
@@ -1272,7 +1272,7 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="8" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="2" spans="1:1" s="15" customFormat="1" x14ac:dyDescent="0.25">
@@ -1366,27 +1366,27 @@
   <sheetData>
     <row r="1" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>29</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>30</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
+        <v>30</v>
+      </c>
+      <c r="B2" t="s">
         <v>31</v>
       </c>
-      <c r="B2" t="s">
+      <c r="C2" t="s">
         <v>32</v>
-      </c>
-      <c r="C2" t="s">
-        <v>33</v>
       </c>
       <c r="D2">
         <v>1</v>
@@ -1394,13 +1394,13 @@
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
+        <v>33</v>
+      </c>
+      <c r="B3" t="s">
         <v>34</v>
       </c>
-      <c r="B3" t="s">
+      <c r="C3" t="s">
         <v>35</v>
-      </c>
-      <c r="C3" t="s">
-        <v>36</v>
       </c>
       <c r="D3">
         <v>1</v>
@@ -1423,16 +1423,16 @@
         <v>0</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C1" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="D1" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="D1" s="7" t="s">
+      <c r="E1" s="7" t="s">
         <v>38</v>
-      </c>
-      <c r="E1" s="7" t="s">
-        <v>39</v>
       </c>
       <c r="F1" s="7" t="s">
         <v>6</v>
@@ -1450,37 +1450,37 @@
         <v>10</v>
       </c>
       <c r="K1" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="L1" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="L1" s="7" t="s">
+      <c r="M1" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="M1" s="7" t="s">
+      <c r="N1" s="7" t="s">
         <v>42</v>
       </c>
-      <c r="N1" s="7" t="s">
+      <c r="O1" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="O1" s="7" t="s">
+      <c r="P1" s="7" t="s">
         <v>44</v>
       </c>
-      <c r="P1" s="7" t="s">
+      <c r="Q1" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="Q1" s="7" t="s">
+      <c r="R1" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="R1" s="7" t="s">
+      <c r="S1" s="8" t="s">
         <v>47</v>
       </c>
-      <c r="S1" s="8" t="s">
+      <c r="T1" s="8" t="s">
         <v>48</v>
       </c>
-      <c r="T1" s="8" t="s">
+      <c r="U1" s="8" t="s">
         <v>49</v>
-      </c>
-      <c r="U1" s="8" t="s">
-        <v>50</v>
       </c>
       <c r="V1" s="8" t="s">
         <v>5</v>
@@ -1525,16 +1525,16 @@
         <v>0</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C1" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="D1" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="D1" s="9" t="s">
+      <c r="E1" s="9" t="s">
         <v>38</v>
-      </c>
-      <c r="E1" s="9" t="s">
-        <v>39</v>
       </c>
       <c r="F1" s="9" t="s">
         <v>6</v>
@@ -1552,37 +1552,37 @@
         <v>10</v>
       </c>
       <c r="K1" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="L1" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="L1" s="7" t="s">
+      <c r="M1" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="M1" s="7" t="s">
+      <c r="N1" s="7" t="s">
         <v>42</v>
       </c>
-      <c r="N1" s="7" t="s">
+      <c r="O1" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="O1" s="7" t="s">
+      <c r="P1" s="7" t="s">
         <v>44</v>
       </c>
-      <c r="P1" s="7" t="s">
+      <c r="Q1" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="Q1" s="7" t="s">
+      <c r="R1" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="R1" s="7" t="s">
+      <c r="S1" s="8" t="s">
         <v>47</v>
       </c>
-      <c r="S1" s="8" t="s">
+      <c r="T1" s="8" t="s">
         <v>48</v>
       </c>
-      <c r="T1" s="8" t="s">
+      <c r="U1" s="8" t="s">
         <v>49</v>
-      </c>
-      <c r="U1" s="8" t="s">
-        <v>50</v>
       </c>
       <c r="V1" s="8" t="s">
         <v>5</v>
@@ -1596,37 +1596,37 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
+        <v>50</v>
+      </c>
+      <c r="C2" t="s">
         <v>51</v>
       </c>
-      <c r="C2" t="s">
+      <c r="D2" t="s">
         <v>52</v>
       </c>
-      <c r="D2" t="s">
+      <c r="E2" t="s">
         <v>53</v>
       </c>
-      <c r="E2" t="s">
+      <c r="F2" t="s">
         <v>54</v>
-      </c>
-      <c r="F2" t="s">
-        <v>55</v>
       </c>
       <c r="G2">
         <v>1083</v>
       </c>
       <c r="H2" t="s">
+        <v>21</v>
+      </c>
+      <c r="I2" t="s">
         <v>22</v>
       </c>
-      <c r="I2" t="s">
+      <c r="J2" t="s">
         <v>23</v>
       </c>
-      <c r="J2" t="s">
-        <v>24</v>
-      </c>
       <c r="M2" t="s">
+        <v>55</v>
+      </c>
+      <c r="O2" t="s">
         <v>56</v>
-      </c>
-      <c r="O2" t="s">
-        <v>57</v>
       </c>
     </row>
     <row r="3" spans="1:23" x14ac:dyDescent="0.25">
@@ -1634,37 +1634,37 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C3" t="s">
+        <v>57</v>
+      </c>
+      <c r="D3" t="s">
         <v>58</v>
       </c>
-      <c r="D3" t="s">
+      <c r="E3" t="s">
         <v>59</v>
       </c>
-      <c r="E3" t="s">
+      <c r="F3" t="s">
         <v>60</v>
-      </c>
-      <c r="F3" t="s">
-        <v>61</v>
       </c>
       <c r="G3">
         <v>9880</v>
       </c>
       <c r="H3" t="s">
+        <v>61</v>
+      </c>
+      <c r="I3" t="s">
+        <v>22</v>
+      </c>
+      <c r="J3" t="s">
+        <v>23</v>
+      </c>
+      <c r="M3" t="s">
         <v>62</v>
       </c>
-      <c r="I3" t="s">
-        <v>23</v>
-      </c>
-      <c r="J3" t="s">
-        <v>24</v>
-      </c>
-      <c r="M3" t="s">
+      <c r="O3" t="s">
         <v>63</v>
-      </c>
-      <c r="O3" t="s">
-        <v>64</v>
       </c>
     </row>
     <row r="4" spans="1:23" x14ac:dyDescent="0.25">
@@ -1672,37 +1672,37 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C4" t="s">
+        <v>64</v>
+      </c>
+      <c r="D4" t="s">
         <v>65</v>
       </c>
-      <c r="D4" t="s">
+      <c r="E4" t="s">
+        <v>59</v>
+      </c>
+      <c r="F4" t="s">
         <v>66</v>
-      </c>
-      <c r="E4" t="s">
-        <v>60</v>
-      </c>
-      <c r="F4" t="s">
-        <v>67</v>
       </c>
       <c r="G4">
         <v>1083</v>
       </c>
       <c r="H4" t="s">
+        <v>21</v>
+      </c>
+      <c r="I4" t="s">
         <v>22</v>
       </c>
-      <c r="I4" t="s">
+      <c r="J4" t="s">
         <v>23</v>
       </c>
-      <c r="J4" t="s">
-        <v>24</v>
-      </c>
       <c r="M4" t="s">
+        <v>67</v>
+      </c>
+      <c r="O4" t="s">
         <v>68</v>
-      </c>
-      <c r="O4" t="s">
-        <v>69</v>
       </c>
     </row>
     <row r="5" spans="1:23" x14ac:dyDescent="0.25">
@@ -1710,40 +1710,40 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C5" t="s">
+        <v>69</v>
+      </c>
+      <c r="D5" t="s">
         <v>70</v>
       </c>
-      <c r="D5" t="s">
+      <c r="E5" t="s">
+        <v>53</v>
+      </c>
+      <c r="F5" t="s">
         <v>71</v>
-      </c>
-      <c r="E5" t="s">
-        <v>54</v>
-      </c>
-      <c r="F5" t="s">
-        <v>72</v>
       </c>
       <c r="G5">
         <v>1083</v>
       </c>
       <c r="H5" t="s">
+        <v>21</v>
+      </c>
+      <c r="I5" t="s">
         <v>22</v>
       </c>
-      <c r="I5" t="s">
+      <c r="J5" t="s">
         <v>23</v>
       </c>
-      <c r="J5" t="s">
-        <v>24</v>
-      </c>
       <c r="K5" t="s">
+        <v>72</v>
+      </c>
+      <c r="M5" s="10" t="s">
         <v>73</v>
       </c>
-      <c r="M5" s="10" t="s">
+      <c r="O5" t="s">
         <v>74</v>
-      </c>
-      <c r="O5" t="s">
-        <v>75</v>
       </c>
     </row>
     <row r="6" spans="1:23" x14ac:dyDescent="0.25">
@@ -1751,40 +1751,40 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C6" t="s">
+        <v>75</v>
+      </c>
+      <c r="D6" t="s">
         <v>76</v>
       </c>
-      <c r="D6" t="s">
+      <c r="E6" t="s">
+        <v>53</v>
+      </c>
+      <c r="F6" t="s">
         <v>77</v>
-      </c>
-      <c r="E6" t="s">
-        <v>54</v>
-      </c>
-      <c r="F6" t="s">
-        <v>78</v>
       </c>
       <c r="G6">
         <v>1083</v>
       </c>
       <c r="H6" t="s">
+        <v>21</v>
+      </c>
+      <c r="I6" t="s">
         <v>22</v>
       </c>
-      <c r="I6" t="s">
+      <c r="J6" t="s">
         <v>23</v>
       </c>
-      <c r="J6" t="s">
-        <v>24</v>
-      </c>
       <c r="K6" t="s">
+        <v>78</v>
+      </c>
+      <c r="M6" s="10" t="s">
         <v>79</v>
       </c>
-      <c r="M6" s="10" t="s">
+      <c r="O6" s="10" t="s">
         <v>80</v>
-      </c>
-      <c r="O6" s="10" t="s">
-        <v>81</v>
       </c>
     </row>
   </sheetData>
@@ -1813,25 +1813,25 @@
         <v>0</v>
       </c>
       <c r="B1" s="8" t="s">
+        <v>81</v>
+      </c>
+      <c r="C1" s="11" t="s">
         <v>82</v>
       </c>
-      <c r="C1" s="11" t="s">
+      <c r="D1" s="11" t="s">
         <v>83</v>
       </c>
-      <c r="D1" s="11" t="s">
+      <c r="E1" s="11" t="s">
         <v>84</v>
       </c>
-      <c r="E1" s="11" t="s">
+      <c r="F1" s="12" t="s">
         <v>85</v>
       </c>
-      <c r="F1" s="12" t="s">
+      <c r="G1" s="12" t="s">
         <v>86</v>
       </c>
-      <c r="G1" s="12" t="s">
+      <c r="H1" s="8" t="s">
         <v>87</v>
-      </c>
-      <c r="H1" s="8" t="s">
-        <v>88</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
@@ -1928,25 +1928,25 @@
   <sheetData>
     <row r="1" spans="1:7" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="8" t="s">
+        <v>88</v>
+      </c>
+      <c r="B1" s="8" t="s">
         <v>89</v>
       </c>
-      <c r="B1" s="8" t="s">
+      <c r="C1" s="8" t="s">
         <v>90</v>
       </c>
-      <c r="C1" s="8" t="s">
+      <c r="D1" s="8" t="s">
         <v>91</v>
       </c>
-      <c r="D1" s="8" t="s">
+      <c r="E1" s="8" t="s">
         <v>92</v>
       </c>
-      <c r="E1" s="8" t="s">
+      <c r="F1" s="8" t="s">
         <v>93</v>
       </c>
-      <c r="F1" s="8" t="s">
+      <c r="G1" s="8" t="s">
         <v>94</v>
-      </c>
-      <c r="G1" s="8" t="s">
-        <v>95</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
@@ -1954,22 +1954,22 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
+        <v>95</v>
+      </c>
+      <c r="C2" t="s">
+        <v>95</v>
+      </c>
+      <c r="D2" t="s">
+        <v>95</v>
+      </c>
+      <c r="E2" t="s">
+        <v>95</v>
+      </c>
+      <c r="F2" t="s">
+        <v>95</v>
+      </c>
+      <c r="G2" t="s">
         <v>96</v>
-      </c>
-      <c r="C2" t="s">
-        <v>96</v>
-      </c>
-      <c r="D2" t="s">
-        <v>96</v>
-      </c>
-      <c r="E2" t="s">
-        <v>96</v>
-      </c>
-      <c r="F2" t="s">
-        <v>96</v>
-      </c>
-      <c r="G2" t="s">
-        <v>97</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -1977,22 +1977,22 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="E3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="F3" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="G3" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
@@ -2000,22 +2000,22 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C4" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D4" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="E4" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="F4" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="G4" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
@@ -2023,22 +2023,22 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C5" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D5" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="E5" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="F5" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="G5" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
@@ -2046,22 +2046,22 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C6" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D6" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="E6" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="F6" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="G6" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
   </sheetData>
@@ -2109,19 +2109,19 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D2">
         <v>1083</v>
       </c>
       <c r="E2" t="s">
+        <v>21</v>
+      </c>
+      <c r="F2" t="s">
         <v>22</v>
-      </c>
-      <c r="F2" t="s">
-        <v>23</v>
       </c>
     </row>
   </sheetData>
@@ -2146,28 +2146,28 @@
         <v>0</v>
       </c>
       <c r="B1" s="11" t="s">
+        <v>101</v>
+      </c>
+      <c r="C1" s="11" t="s">
         <v>102</v>
       </c>
-      <c r="C1" s="11" t="s">
+      <c r="D1" s="11" t="s">
         <v>103</v>
       </c>
-      <c r="D1" s="11" t="s">
+      <c r="E1" s="11" t="s">
         <v>104</v>
       </c>
-      <c r="E1" s="11" t="s">
+      <c r="F1" s="11" t="s">
         <v>105</v>
       </c>
-      <c r="F1" s="11" t="s">
+      <c r="G1" s="11" t="s">
         <v>106</v>
       </c>
-      <c r="G1" s="11" t="s">
+      <c r="H1" s="11" t="s">
         <v>107</v>
       </c>
-      <c r="H1" s="11" t="s">
+      <c r="I1" s="11" t="s">
         <v>108</v>
-      </c>
-      <c r="I1" s="11" t="s">
-        <v>109</v>
       </c>
       <c r="J1" s="11" t="s">
         <v>3</v>
@@ -2178,10 +2178,10 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
+        <v>109</v>
+      </c>
+      <c r="C2" t="s">
         <v>110</v>
-      </c>
-      <c r="C2" t="s">
-        <v>111</v>
       </c>
       <c r="D2">
         <v>1</v>
@@ -2192,10 +2192,10 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C3" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="D3">
         <v>1</v>
@@ -2206,10 +2206,10 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C4" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="D4">
         <v>1</v>
@@ -2220,10 +2220,10 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="C5" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="D5">
         <v>1</v>
@@ -2234,10 +2234,10 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C6" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="D6">
         <v>1</v>
@@ -2248,10 +2248,10 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C7" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="D7">
         <v>1</v>
@@ -2262,10 +2262,10 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C8" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="D8">
         <v>1</v>
@@ -2276,10 +2276,10 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
+        <v>117</v>
+      </c>
+      <c r="C9" t="s">
         <v>118</v>
-      </c>
-      <c r="C9" t="s">
-        <v>119</v>
       </c>
       <c r="D9">
         <v>1</v>
@@ -2290,10 +2290,10 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C10" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D10">
         <v>1</v>
@@ -2304,10 +2304,10 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
+        <v>120</v>
+      </c>
+      <c r="C11" t="s">
         <v>121</v>
-      </c>
-      <c r="C11" t="s">
-        <v>122</v>
       </c>
       <c r="D11">
         <v>1</v>
@@ -2321,10 +2321,10 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C12" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="D12">
         <v>1</v>
@@ -2338,10 +2338,10 @@
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C13" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="D13">
         <v>1</v>
@@ -2355,10 +2355,10 @@
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C14" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="D14">
         <v>1</v>
@@ -2372,10 +2372,10 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C15" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="D15">
         <v>1</v>
@@ -2404,16 +2404,16 @@
   <sheetData>
     <row r="1" spans="1:4" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="8" t="s">
+        <v>126</v>
+      </c>
+      <c r="B1" s="8" t="s">
+        <v>88</v>
+      </c>
+      <c r="C1" s="8" t="s">
         <v>127</v>
       </c>
-      <c r="B1" s="8" t="s">
-        <v>89</v>
-      </c>
-      <c r="C1" s="8" t="s">
+      <c r="D1" s="8" t="s">
         <v>128</v>
-      </c>
-      <c r="D1" s="8" t="s">
-        <v>129</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">

--- a/fmt/tests/condominium_import.xlsx
+++ b/fmt/tests/condominium_import.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\DEV\wamp64\www\fmt-yb\packages\fmt\tests\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D761F1A-AB86-4B8A-A6C3-7D22E5134BB3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8EDE749D-DFFC-4837-8DFC-BD20ABB67AEE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="45" windowWidth="28800" windowHeight="15435" tabRatio="739" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="739" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Condominium" sheetId="1" r:id="rId1"/>
@@ -32,11 +32,11 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Condominium!$A$1:$R$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">Lots!$A$1:$J$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">Owners!$A$1:$W$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">Ownerships!$A$1:$H$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">Ownerships!$A$1:$I$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">Ownerships_com_prefs!$A$1:$G$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">Ownerships_history!$A$1:$G$1</definedName>
   </definedNames>
-  <calcPr calcId="0" iterateDelta="1E-4"/>
+  <calcPr calcId="0"/>
   <extLst>
     <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
       <loext:extCalcPr stringRefSyntax="ExcelA1"/>
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="251" uniqueCount="137">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="252" uniqueCount="138">
   <si>
     <t>code</t>
   </si>
@@ -457,6 +457,9 @@
   </si>
   <si>
     <t>manager_code</t>
+  </si>
+  <si>
+    <t>shares_total</t>
   </si>
 </sst>
 </file>
@@ -533,7 +536,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -574,6 +577,9 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1796,19 +1802,19 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
-  <dimension ref="A1:H6"/>
+  <dimension ref="A1:I6"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="16.42578125" customWidth="1"/>
     <col min="2" max="2" width="13.140625" customWidth="1"/>
     <col min="3" max="3" width="23.28515625" customWidth="1"/>
     <col min="4" max="4" width="23.85546875" customWidth="1"/>
-    <col min="5" max="5" width="18.28515625" customWidth="1"/>
-    <col min="6" max="7" width="31.140625" customWidth="1"/>
-    <col min="8" max="8" width="23" customWidth="1"/>
+    <col min="5" max="6" width="18.28515625" customWidth="1"/>
+    <col min="7" max="8" width="31.140625" customWidth="1"/>
+    <col min="9" max="9" width="23" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="8" t="s">
         <v>0</v>
       </c>
@@ -1824,17 +1830,20 @@
       <c r="E1" s="11" t="s">
         <v>84</v>
       </c>
-      <c r="F1" s="12" t="s">
+      <c r="F1" s="18" t="s">
+        <v>137</v>
+      </c>
+      <c r="G1" s="12" t="s">
         <v>85</v>
       </c>
-      <c r="G1" s="12" t="s">
+      <c r="H1" s="12" t="s">
         <v>86</v>
       </c>
-      <c r="H1" s="8" t="s">
+      <c r="I1" s="8" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>1</v>
       </c>
@@ -1847,8 +1856,11 @@
       <c r="F2">
         <v>1</v>
       </c>
-    </row>
-    <row r="3" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>2</v>
       </c>
@@ -1859,10 +1871,13 @@
         <v>1</v>
       </c>
       <c r="F3">
+        <v>1</v>
+      </c>
+      <c r="G3">
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>3</v>
       </c>
@@ -1873,10 +1888,13 @@
         <v>1</v>
       </c>
       <c r="F4">
+        <v>1</v>
+      </c>
+      <c r="G4">
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>4</v>
       </c>
@@ -1887,10 +1905,13 @@
         <v>1</v>
       </c>
       <c r="F5">
+        <v>1</v>
+      </c>
+      <c r="G5">
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>5</v>
       </c>
@@ -1901,11 +1922,14 @@
         <v>1</v>
       </c>
       <c r="F6">
+        <v>1</v>
+      </c>
+      <c r="G6">
         <v>5</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H1" xr:uid="{00000000-0009-0000-0000-000004000000}"/>
+  <autoFilter ref="A1:I1" xr:uid="{00000000-0009-0000-0000-000004000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
